--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="29" customWidth="1" min="3" max="3"/>
@@ -1078,12 +1078,27 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>emotion1</t>
+          <t>statename1</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>emotion2</t>
+          <t>statename2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>slotstateid1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>slotstateid2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>##备注</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1135,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1176,12 +1201,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>表情1</t>
+          <t>左说话人状态名</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>表情2</t>
+          <t>右说话人状态名</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>说话人1插槽状态外键</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>说话人2插槽状态外键</t>
         </is>
       </c>
     </row>
@@ -1203,6 +1238,22 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1221,6 +1272,22 @@
       </c>
       <c r="F6" t="n">
         <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1241,6 +1308,22 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>think1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2001</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1260,6 +1343,22 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1279,6 +1378,22 @@
       <c r="F9" t="n">
         <v>5</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1298,6 +1413,22 @@
       <c r="F10" t="n">
         <v>6</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -1317,6 +1448,22 @@
       <c r="F11" t="n">
         <v>7</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>think2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -1336,6 +1483,22 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -1355,6 +1518,22 @@
       <c r="F13" t="n">
         <v>9</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>think3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2001</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -1374,6 +1553,12 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -1393,6 +1578,12 @@
       <c r="F15" t="n">
         <v>2</v>
       </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -1412,6 +1603,12 @@
       <c r="F16" t="n">
         <v>3</v>
       </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
@@ -1431,6 +1628,12 @@
       <c r="F17" t="n">
         <v>4</v>
       </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
@@ -1450,6 +1653,12 @@
       <c r="F18" t="n">
         <v>5</v>
       </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
@@ -1469,6 +1678,12 @@
       <c r="F19" t="n">
         <v>6</v>
       </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -1488,6 +1703,12 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
@@ -1507,6 +1728,12 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
@@ -1526,10 +1753,10 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1551,10 +1778,10 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1576,10 +1803,10 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1601,10 +1828,10 @@
       <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1626,10 +1853,10 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1651,10 +1878,10 @@
       <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1676,10 +1903,10 @@
       <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1701,10 +1928,10 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1726,10 +1953,10 @@
       <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1751,10 +1978,10 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1776,10 +2003,10 @@
       <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1801,10 +2028,10 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1826,10 +2053,10 @@
       <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1851,10 +2078,10 @@
       <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1876,10 +2103,10 @@
       <c r="F36" t="n">
         <v>2</v>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1901,10 +2128,10 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1926,10 +2153,10 @@
       <c r="F38" t="n">
         <v>2</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1951,10 +2178,10 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1976,10 +2203,10 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2001,10 +2228,10 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2026,10 +2253,10 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2051,10 +2278,10 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2076,10 +2303,10 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2101,10 +2328,10 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2126,10 +2353,10 @@
       <c r="F46" t="n">
         <v>2</v>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2151,10 +2378,10 @@
       <c r="F47" t="n">
         <v>3</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2176,10 +2403,10 @@
       <c r="F48" t="n">
         <v>4</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2201,10 +2428,10 @@
       <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2226,11 +2453,71 @@
       <c r="F50" t="n">
         <v>6</v>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>406</v>
+      </c>
+      <c r="C51" t="n">
+        <v>400</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>你决定去地下竞技场看看。</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>407</v>
+      </c>
+      <c r="C52" t="n">
+        <v>400</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>来吧，让我看看你的实力。</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A35D5-F4D2-4A58-9F20-2897D84A4E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="dialogcontent" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -149,6 +151,9 @@
     <t>哦！哦，操，哦，哦，不，哦······</t>
   </si>
   <si>
+    <t>angry</t>
+  </si>
+  <si>
     <t>操你，唉，为什么！我是说，&lt;color=red&gt;嗯？&lt;/color&gt;</t>
   </si>
   <si>
@@ -261,17 +266,19 @@
   </si>
   <si>
     <t>来吧，让我看看你的实力。</t>
-  </si>
-  <si>
-    <t>angry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,29 +287,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -310,28 +633,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -616,21 +1225,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="33.5" customWidth="1"/>
-    <col min="5" max="5" width="54.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="54.8796296296296" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="17.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,7 +1276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -697,7 +1308,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -705,7 +1316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -737,7 +1348,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" ht="28.8" spans="1:11">
       <c r="B5">
         <v>1</v>
       </c>
@@ -766,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" ht="28.8" spans="1:11">
       <c r="B6">
         <v>2</v>
       </c>
@@ -795,7 +1406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" ht="28.8" spans="1:11">
       <c r="B7">
         <v>3</v>
       </c>
@@ -824,7 +1435,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11">
       <c r="B8">
         <v>4</v>
       </c>
@@ -853,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="9" ht="28.8" spans="1:11">
       <c r="B9">
         <v>5</v>
       </c>
@@ -882,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="10" ht="28.8" spans="1:11">
       <c r="B10">
         <v>6</v>
       </c>
@@ -911,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11">
       <c r="B11">
         <v>7</v>
       </c>
@@ -940,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11">
       <c r="B12">
         <v>8</v>
       </c>
@@ -969,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="13" ht="28.8" spans="1:11">
       <c r="B13">
         <v>9</v>
       </c>
@@ -998,7 +1609,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11">
       <c r="B14">
         <v>10</v>
       </c>
@@ -1018,7 +1629,7 @@
         <v>28</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1027,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11">
       <c r="B15">
         <v>11</v>
       </c>
@@ -1038,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -1047,7 +1658,7 @@
         <v>28</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1056,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11">
       <c r="B16">
         <v>12</v>
       </c>
@@ -1067,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -1085,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="17" ht="28.8" spans="2:10">
       <c r="B17">
         <v>13</v>
       </c>
@@ -1096,7 +1707,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1114,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="18" ht="28.8" spans="2:10">
       <c r="B18">
         <v>14</v>
       </c>
@@ -1125,7 +1736,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -1143,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:10">
       <c r="B19">
         <v>15</v>
       </c>
@@ -1154,7 +1765,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -1172,7 +1783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="20" ht="28.8" spans="2:10">
       <c r="B20">
         <v>16</v>
       </c>
@@ -1183,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1201,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="21" ht="28.8" spans="2:10">
       <c r="B21">
         <v>17</v>
       </c>
@@ -1212,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1230,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:10">
       <c r="B22">
         <v>100</v>
       </c>
@@ -1241,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1253,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:10">
       <c r="B23">
         <v>101</v>
       </c>
@@ -1264,7 +1875,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -1276,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:10">
       <c r="B24">
         <v>102</v>
       </c>
@@ -1287,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -1299,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:10">
       <c r="B25">
         <v>103</v>
       </c>
@@ -1310,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F25">
         <v>4</v>
@@ -1322,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="26" ht="28.8" spans="2:10">
       <c r="B26">
         <v>104</v>
       </c>
@@ -1333,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1345,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:10">
       <c r="B27">
         <v>105</v>
       </c>
@@ -1356,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -1368,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:10">
       <c r="B28">
         <v>106</v>
       </c>
@@ -1379,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -1391,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:10">
       <c r="B29">
         <v>200</v>
       </c>
@@ -1402,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1414,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:10">
       <c r="B30">
         <v>201</v>
       </c>
@@ -1425,7 +2036,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F30">
         <v>2</v>
@@ -1437,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:10">
       <c r="B31">
         <v>202</v>
       </c>
@@ -1448,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1460,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:10">
       <c r="B32">
         <v>203</v>
       </c>
@@ -1471,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -1483,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:10">
       <c r="B33">
         <v>204</v>
       </c>
@@ -1494,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1506,7 +2117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:10">
       <c r="B34">
         <v>205</v>
       </c>
@@ -1517,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -1529,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="35" ht="28.8" spans="2:10">
       <c r="B35">
         <v>206</v>
       </c>
@@ -1540,7 +2151,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -1552,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:10">
       <c r="B36">
         <v>207</v>
       </c>
@@ -1563,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F36">
         <v>2</v>
@@ -1575,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:10">
       <c r="B37">
         <v>300</v>
       </c>
@@ -1586,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -1598,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:10">
       <c r="B38">
         <v>301</v>
       </c>
@@ -1609,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -1621,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:10">
       <c r="B39">
         <v>302</v>
       </c>
@@ -1632,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1644,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:10">
       <c r="B40">
         <v>303</v>
       </c>
@@ -1655,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -1667,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="41" ht="43.2" spans="2:10">
       <c r="B41">
         <v>304</v>
       </c>
@@ -1678,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -1690,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:10">
       <c r="B42">
         <v>305</v>
       </c>
@@ -1701,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F42">
         <v>2</v>
@@ -1713,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="43" ht="28.8" spans="2:10">
       <c r="B43">
         <v>306</v>
       </c>
@@ -1724,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -1736,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:10">
       <c r="B44">
         <v>307</v>
       </c>
@@ -1747,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -1759,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:10">
       <c r="B45">
         <v>400</v>
       </c>
@@ -1770,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -1782,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:10">
       <c r="B46">
         <v>401</v>
       </c>
@@ -1793,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -1805,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:10">
       <c r="B47">
         <v>402</v>
       </c>
@@ -1816,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -1828,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:10">
       <c r="B48">
         <v>403</v>
       </c>
@@ -1839,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F48">
         <v>4</v>
@@ -1851,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="49" ht="28.8" spans="2:10">
       <c r="B49">
         <v>404</v>
       </c>
@@ -1862,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F49">
         <v>5</v>
@@ -1874,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:10">
       <c r="B50">
         <v>405</v>
       </c>
@@ -1885,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F50">
         <v>6</v>
@@ -1897,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:10">
       <c r="B51">
         <v>406</v>
       </c>
@@ -1908,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F51">
         <v>7</v>
@@ -1917,13 +2528,13 @@
         <v>28</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52">
         <v>407</v>
       </c>
@@ -1934,7 +2545,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F52">
         <v>8</v>
@@ -1943,14 +2554,14 @@
         <v>33</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF9D567-91E0-4961-9FA8-D388D94C632A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C107A1-D092-4332-9139-D44C71BAD332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1038,7 +1038,7 @@
         <v>79</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1061,7 +1061,7 @@
         <v>39</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1090,7 +1090,7 @@
         <v>41</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1119,7 +1119,7 @@
         <v>42</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1148,7 +1148,7 @@
         <v>43</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
@@ -1177,7 +1177,7 @@
         <v>44</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1206,7 +1206,7 @@
         <v>45</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.125" customWidth="1" style="5" min="1" max="1"/>
@@ -558,6 +558,11 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>gain_item_text</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>##备注</t>
         </is>
       </c>
@@ -644,6 +649,11 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -712,6 +722,11 @@
       <c r="J4" s="5" t="inlineStr">
         <is>
           <t>说话人2插槽状态外键</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>获得物品提示文本</t>
         </is>
       </c>
     </row>
@@ -2195,6 +2210,264 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>52</v>
+      </c>
+      <c r="C57" t="n">
+        <v>500</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>河马走进了训练场</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>53</v>
+      </c>
+      <c r="C58" t="n">
+        <v>500</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>教练，给我一把武器吧！</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>54</v>
+      </c>
+      <c r="C59" t="n">
+        <v>500</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>好吧，这把铁剑给你。</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>获得：铁剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>55</v>
+      </c>
+      <c r="C60" t="n">
+        <v>500</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>太好了！我收下了。</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>获得：护盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>56</v>
+      </c>
+      <c r="C61" t="n">
+        <v>500</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>河马获得了装备，战斗力大增。</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>57</v>
+      </c>
+      <c r="C62" t="n">
+        <v>500</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>不错，现在去实战吧！</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>获得：经验药水×3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.125" customWidth="1" style="5" min="1" max="1"/>
@@ -2228,8 +2228,6 @@
       <c r="F57" t="n">
         <v>1</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -2239,17 +2237,12 @@
       <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" t="n">
@@ -2269,8 +2262,6 @@
       <c r="F58" t="n">
         <v>2</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -2280,17 +2271,12 @@
       <c r="K58" t="n">
         <v>0</v>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" t="n">
@@ -2310,8 +2296,6 @@
       <c r="F59" t="n">
         <v>3</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -2321,16 +2305,12 @@
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>获得：铁剑</t>
@@ -2355,8 +2335,6 @@
       <c r="F60" t="n">
         <v>4</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -2366,16 +2344,12 @@
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>获得：护盾</t>
@@ -2400,8 +2374,6 @@
       <c r="F61" t="n">
         <v>5</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -2411,17 +2383,12 @@
       <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" t="n">
@@ -2441,8 +2408,6 @@
       <c r="F62" t="n">
         <v>6</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -2452,19 +2417,135 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>获得：经验药水×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>58</v>
+      </c>
+      <c r="C63" t="n">
+        <v>600</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>获得剑x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>59</v>
+      </c>
+      <c r="C64" t="n">
+        <v>600</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>获得黄金战斧一把x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>60</v>
+      </c>
+      <c r="C65" t="n">
+        <v>600</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>获得传说中的附魔剑碎片一份x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>61</v>
+      </c>
+      <c r="C66" t="n">
+        <v>600</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>获得天地玄黄宇宙洪荒中的绝世宝物一枚x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>62</v>
+      </c>
+      <c r="C67" t="n">
+        <v>600</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十一二三四五六七八九十</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>获得剑x1</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E0E9FB-4F5F-40FB-95DE-23E5923157DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E834A19E-53F8-4E8C-B7C0-3748BA46AAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -200,109 +200,145 @@
     <t>9之后的数字应该是10。</t>
   </si>
   <si>
+    <t>一拳打在他脸上！&lt;br&gt;教练这下惨了，你的拳头在他的嘴里过了个来回，他昨天吃的花生米都被打的爆了一地，估计他2年内没法再吃花生米了。</t>
+  </si>
+  <si>
+    <t>获得了两颗打豁进去的牙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是这样的，我需要你帮我个忙。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么事？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许我们应该说现在是朋克城紧急事态。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看到台子上的那个家伙了吗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>操你，唉，为什么！我是说，&lt;color=red&gt;嗯？&lt;/color&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>朋克城外面的家伙有一半对他的拳头&lt;color=red&gt;过敏&lt;/color&gt;，另一半人身上的石膏还没卸下来呢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他是拳王石头·球儿，一个兢兢业业的王八蛋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>外城的人每天无所事事，除了坐在这里看拳王把别人打的&lt;color=red&gt;满地找牙&lt;/color&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你要想进到朋克城里面，就必须让拳赛重新开起来</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个家伙看着像个知名人物，你好像在某个杂志上见过，不过那个时候你去看下一页的笑话栏目了，那个笑话很烂。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>外城里所有家伙打成一团，你看到他们在拳击擂台下面滚来滚去，台子下面堆着挑战者，他们都让拳王给打瘪了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是现在不行了，方圆百里内的所有人都给打成缺牙齿了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这的规矩是只有牙齿齐全的人才能上场挨揍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>要是拳赛开不起来，所有外城人就会闲下来，然后抱着某种使命互相殴打</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>去找一套牙给他们用或者随你的便想个什么别的办法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>操，他们为啥不自己去找</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呃，他们正忙着在地上捡自己的牙，暂时应该不太有空</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哦哟！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>talk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>idle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>是吗，我觉得至少不应该是9，不过我建议你藏好这个秘密，9之后的数字或许会在朋克城引起恐慌。</t>
-  </si>
-  <si>
-    <t>一拳打在他脸上！&lt;br&gt;教练这下惨了，你的拳头在他的嘴里过了个来回，他昨天吃的花生米都被打的爆了一地，估计他2年内没法再吃花生米了。</t>
-  </si>
-  <si>
-    <t>获得了两颗打豁进去的牙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是这样的，我需要你帮我个忙。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>什么事？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>或许我们应该说现在是朋克城紧急事态。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你看到台子上的那个家伙了吗</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>操你，唉，为什么！我是说，&lt;color=red&gt;嗯？&lt;/color&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>朋克城外面的家伙有一半对他的拳头&lt;color=red&gt;过敏&lt;/color&gt;，另一半人身上的石膏还没卸下来呢</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他是拳王石头·球儿，一个兢兢业业的王八蛋</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>外城的人每天无所事事，除了坐在这里看拳王把别人打的&lt;color=red&gt;满地找牙&lt;/color&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你要想进到朋克城里面，就必须让拳赛重新开起来</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个家伙看着像个知名人物，你好像在某个杂志上见过，不过那个时候你去看下一页的笑话栏目了，那个笑话很烂。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>外城里所有家伙打成一团，你看到他们在拳击擂台下面滚来滚去，台子下面堆着挑战者，他们都让拳王给打瘪了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>但是现在不行了，方圆百里内的所有人都给打成缺牙齿了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这的规矩是只有牙齿齐全的人才能上场挨揍</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>要是拳赛开不起来，所有外城人就会闲下来，然后抱着某种使命互相殴打</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>去找一套牙给他们用或者随你的便想个什么别的办法</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>操，他们为啥不自己去找</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>呃，他们正忙着在地上捡自己的牙，暂时应该不太有空</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>女子口吧</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哦哟！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>就像这样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到办法了吗，外城人开始发扬自己的想象力了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>talk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>idle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一只鞋子从你们的头顶飞了过去，教练闪身躲避，它打着旋砸在了另一个外城人的头上，你看不见他的正脸，不过应该是给砸的够呛了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一只鞋子从你们的头顶飞了过去，教练闪身躲避，它打着旋砸在了另一个外城人的头上。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那需要多久？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一会我可以帮你问问他们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过愿意回答问题的那帮人还睡着呢，可能得一阵子才行，我估计至少七八天吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真操蛋，现在我们只能等选手们的牙自然痊愈了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>彳亍口吧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到办法了吗，外城人在&lt;color=red&gt;互相殴打&lt;/color&gt;这件事上开始把自己的想象力发扬光大了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看看，我刚才说什么来着，就像这样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呃，呃，其实我暂时还没有什么发现。</t>
+  </si>
+  <si>
+    <t>所以你有带来什么好消息吗，或者不那么好的消息也行，还是说你只是很享受看这些人照着别人的脸擂。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看没个七八个月不成。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练回过头看了眼这个照着脸擂主题乐园里面疲惫不堪的游客们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不，以我的经验而言，拳王的哄睡服务售后一般会持续七八年。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -366,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -396,6 +432,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" customWidth="1"/>
@@ -1147,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -1188,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.15">
@@ -1202,7 +1241,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="3">
         <v>3</v>
@@ -1433,8 +1472,8 @@
       <c r="D24" s="3">
         <v>2</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>57</v>
+      <c r="E24" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="F24" s="3">
         <v>2</v>
@@ -1463,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F25" s="8">
         <v>1</v>
@@ -1492,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="8">
         <v>2</v>
@@ -1521,7 +1560,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F27" s="8">
         <v>3</v>
@@ -1550,7 +1589,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F28" s="8">
         <v>4</v>
@@ -1579,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F29" s="8">
         <v>5</v>
@@ -1608,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F30" s="8">
         <v>6</v>
@@ -1637,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F31" s="8">
         <v>7</v>
@@ -1666,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F32" s="8">
         <v>8</v>
@@ -1695,7 +1734,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" s="8">
         <v>9</v>
@@ -1724,7 +1763,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="8">
         <v>10</v>
@@ -1753,7 +1792,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="8">
         <v>11</v>
@@ -1782,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="8">
         <v>12</v>
@@ -1811,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="8">
         <v>13</v>
@@ -1840,7 +1879,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F38" s="8">
         <v>14</v>
@@ -1869,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39" s="8">
         <v>15</v>
@@ -1898,7 +1937,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F40" s="8">
         <v>16</v>
@@ -1927,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F41" s="8">
         <v>17</v>
@@ -1945,7 +1984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B42" s="10">
         <v>38</v>
       </c>
@@ -1956,16 +1995,16 @@
         <v>2</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1974,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:10" ht="27" x14ac:dyDescent="0.15">
       <c r="B43" s="10">
         <v>39</v>
       </c>
@@ -1985,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F43" s="3">
         <v>2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -2014,16 +2053,16 @@
         <v>1</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F44" s="3">
         <v>3</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
@@ -2043,26 +2082,284 @@
         <v>2</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F45" s="3">
         <v>4</v>
       </c>
       <c r="G45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B46" s="10">
+        <v>42</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1003001</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="8">
+        <v>43</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="8">
+        <v>1</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="8">
+        <v>44</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D48" s="8">
+        <v>2</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="8">
+        <v>2</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="8">
+        <v>45</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="8">
+        <v>3</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="8">
+        <v>46</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D50" s="8">
+        <v>2</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B46" s="10"/>
+      <c r="F50" s="8">
+        <v>4</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="B51" s="8">
+        <v>47</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D51" s="8">
+        <v>2</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F51" s="8">
+        <v>5</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="8">
+        <v>48</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D52" s="8">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" s="8">
+        <v>6</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I52" s="8">
+        <v>0</v>
+      </c>
+      <c r="J52" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="B53" s="8">
+        <v>49</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="8">
+        <v>7</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="8">
+        <v>50</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1003003</v>
+      </c>
+      <c r="D54" s="8">
+        <v>2</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="8">
+        <v>8</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I54" s="8">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E834A19E-53F8-4E8C-B7C0-3748BA46AAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C092F8B-3530-4DFD-B01C-15FBB37F5253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="111">
   <si>
     <t>##var</t>
   </si>
@@ -339,6 +339,77 @@
   </si>
   <si>
     <t>不，以我的经验而言，拳王的哄睡服务售后一般会持续七八年。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练漏出坚毅的眼神。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>angry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>几年前我就找不到这东西了，我还以为早让人拿去擤鼻涕了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看到教练耐人寻味的表情之后决定补上临门一脚。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头·球儿已经失眠很久了，我觉得需要有人教他怎么样才能睡得香。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>就算以朋克城的文学素养为标准来看，这篇报道也是神乎其技的狗屁不通。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你把找到的&lt;color=red&gt;报道&lt;/color&gt;递给了教练&lt;br&gt;他大吃一惊，手差点把自己衣服的口袋捅漏了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>何以见得？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练皱起眉头。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…&lt;color=red&gt;拳王骨裂&lt;/color&gt;在重拳击倒了对手之后，还顺手打废了来拉架的3个裁判和12个粉丝，甚至门口的狗也被打的拉了一地。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真是一个外城的传奇，一己之力促成了外城联赛的去裁判化运动。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他已经退休了至少有3年，这段时间都够观众们互相打死几茬了，所以识货的粉丝再也找不到了，石头·球儿彻底接替了他的位置。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不对，我看拳王骨裂远远称不上退休。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>外城从来没发过退休金，所以他最多只能算是在休息，藏在外面的历史垃圾堆里度过他操蛋的悠长假期。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>透露给你一个好消息。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王骨裂即将回到他忠诚的外城联赛。</t>
+  </si>
+  <si>
+    <t>哇哦，酷。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" customWidth="1"/>
@@ -2361,6 +2432,470 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B55" s="3">
+        <v>51</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="3">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B56" s="3">
+        <v>52</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="3">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B57" s="3">
+        <v>54</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B58" s="3">
+        <v>55</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D58" s="3">
+        <v>1</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B59" s="3">
+        <v>56</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B60" s="3">
+        <v>57</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F60" s="3">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B61" s="3">
+        <v>58</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D61" s="3">
+        <v>2</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F61" s="3">
+        <v>7</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B62" s="3">
+        <v>59</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F62" s="3">
+        <v>8</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B63" s="3">
+        <v>60</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F63" s="3">
+        <v>9</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B64" s="3">
+        <v>61</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F64" s="3">
+        <v>10</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B65" s="3">
+        <v>62</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="3">
+        <v>11</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="B66" s="3">
+        <v>63</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F66" s="3">
+        <v>12</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B67" s="3">
+        <v>64</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D67" s="3">
+        <v>0</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="3">
+        <v>13</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B68" s="3">
+        <v>65</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D68" s="3">
+        <v>2</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68" s="3">
+        <v>14</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B69" s="3">
+        <v>66</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D69" s="3">
+        <v>2</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F69" s="3">
+        <v>15</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B70" s="3">
+        <v>67</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1003004</v>
+      </c>
+      <c r="D70" s="3">
+        <v>1</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F70" s="3">
+        <v>16</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C092F8B-3530-4DFD-B01C-15FBB37F5253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B4DB0D-E083-412A-9E17-EF96899CB1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="122">
   <si>
     <t>##var</t>
   </si>
@@ -410,6 +410,50 @@
   </si>
   <si>
     <t>哇哦，酷。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我可以报名吗，我想成为一个伟大的人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然可以，光屁股，不过你确定吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练喜悦之余带有一点疑虑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>按理来说我们应该搞个好像叫合铜的东西，不过我其实不会写字，所以还是算了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总之你需要知道一件事，呃…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你被打残了，请不要来找我们，如果你被打死了，请你的鬼魂也不要来找我们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太好了！到擂台边上，准备开打吧！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>又一位挑战者！又一位挑战者！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练对着整个场馆的人大喊，外城人停下了斗殴鼻青脸肿的围在擂台旁边，属于外城的摇滚要开始了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快说吧，别他妈废话了。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -810,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" customWidth="1"/>
@@ -2896,6 +2940,325 @@
         <v>0</v>
       </c>
     </row>
+    <row r="71" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B71" s="8">
+        <v>68</v>
+      </c>
+      <c r="C71" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D71" s="8">
+        <v>1</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F71" s="8">
+        <v>17</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I71" s="8">
+        <v>0</v>
+      </c>
+      <c r="J71" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B72" s="8">
+        <v>69</v>
+      </c>
+      <c r="C72" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D72" s="8">
+        <v>2</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F72" s="8">
+        <v>18</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I72" s="8">
+        <v>0</v>
+      </c>
+      <c r="J72" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B73" s="8">
+        <v>70</v>
+      </c>
+      <c r="C73" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D73" s="8">
+        <v>0</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F73" s="8">
+        <v>19</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I73" s="8">
+        <v>0</v>
+      </c>
+      <c r="J73" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="B74" s="8">
+        <v>71</v>
+      </c>
+      <c r="C74" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D74" s="8">
+        <v>2</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" s="8">
+        <v>20</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74" s="8">
+        <v>0</v>
+      </c>
+      <c r="J74" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B75" s="8">
+        <v>72</v>
+      </c>
+      <c r="C75" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D75" s="8">
+        <v>2</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75" s="8">
+        <v>21</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I75" s="8">
+        <v>0</v>
+      </c>
+      <c r="J75" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B76" s="8">
+        <v>73</v>
+      </c>
+      <c r="C76" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D76" s="8">
+        <v>1</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F76" s="8">
+        <v>22</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I76" s="8">
+        <v>0</v>
+      </c>
+      <c r="J76" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="B77" s="8">
+        <v>74</v>
+      </c>
+      <c r="C77" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D77" s="8">
+        <v>2</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F77" s="8">
+        <v>23</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" s="8">
+        <v>0</v>
+      </c>
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B78" s="8">
+        <v>75</v>
+      </c>
+      <c r="C78" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D78" s="8">
+        <v>1</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F78" s="8">
+        <v>24</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I78" s="8">
+        <v>0</v>
+      </c>
+      <c r="J78" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B79" s="8">
+        <v>76</v>
+      </c>
+      <c r="C79" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D79" s="8">
+        <v>2</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F79" s="8">
+        <v>25</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" s="8">
+        <v>0</v>
+      </c>
+      <c r="J79" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="8">
+        <v>77</v>
+      </c>
+      <c r="C80" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F80" s="8">
+        <v>26</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I80" s="8">
+        <v>0</v>
+      </c>
+      <c r="J80" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="B81" s="8">
+        <v>78</v>
+      </c>
+      <c r="C81" s="8">
+        <v>1003005</v>
+      </c>
+      <c r="D81" s="8">
+        <v>0</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F81" s="8">
+        <v>27</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I81" s="8">
+        <v>0</v>
+      </c>
+      <c r="J81" s="8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B4DB0D-E083-412A-9E17-EF96899CB1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D6D4E0-CBE1-4E10-9411-3096861809F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="123">
   <si>
     <t>##var</t>
   </si>
@@ -454,6 +454,10 @@
   </si>
   <si>
     <t>快说吧，别他妈废话了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>catchdog</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -481,12 +485,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1374,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B17" s="3">
         <v>13</v>
       </c>
@@ -1403,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3">
         <v>14</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3">
         <v>15</v>
       </c>
@@ -1461,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B20" s="3">
         <v>16</v>
       </c>
@@ -1490,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="3">
         <v>17</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3">
         <v>18</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="3">
         <v>19</v>
       </c>
@@ -1577,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3">
         <v>20</v>
       </c>
@@ -1606,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B25" s="8">
         <v>21</v>
       </c>
@@ -1634,8 +1640,11 @@
       <c r="J25" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="Q25" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B26" s="8">
         <v>22</v>
       </c>
@@ -1664,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
         <v>23</v>
       </c>
@@ -1693,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="8">
         <v>24</v>
       </c>
@@ -1722,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="8">
         <v>25</v>
       </c>
@@ -1751,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="8">
         <v>26</v>
       </c>
@@ -1780,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B31" s="8">
         <v>27</v>
       </c>
@@ -1809,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B32" s="8">
         <v>28</v>
       </c>
@@ -1838,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B33" s="8">
         <v>29</v>
       </c>
@@ -1867,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B34" s="8">
         <v>30</v>
       </c>
@@ -1896,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B35" s="8">
         <v>31</v>
       </c>
@@ -1925,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B36" s="8">
         <v>32</v>
       </c>
@@ -1954,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="8">
         <v>33</v>
       </c>
@@ -1983,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="8">
         <v>34</v>
       </c>
@@ -2012,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B39" s="8">
         <v>35</v>
       </c>
@@ -2041,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="8">
         <v>36</v>
       </c>
@@ -2070,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="8">
         <v>37</v>
       </c>
@@ -2099,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B42" s="10">
         <v>38</v>
       </c>
@@ -2127,8 +2136,11 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="Q42" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B43" s="10">
         <v>39</v>
       </c>
@@ -2157,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="10">
         <v>40</v>
       </c>
@@ -2186,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="10">
         <v>41</v>
       </c>
@@ -2215,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B46" s="10">
         <v>42</v>
       </c>
@@ -2244,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="8">
         <v>43</v>
       </c>
@@ -2273,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="8">
         <v>44</v>
       </c>
@@ -2302,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="8">
         <v>45</v>
       </c>
@@ -2331,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8">
         <v>46</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B51" s="8">
         <v>47</v>
       </c>
@@ -2389,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="8">
         <v>48</v>
       </c>
@@ -2418,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B53" s="8">
         <v>49</v>
       </c>
@@ -2447,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B54" s="8">
         <v>50</v>
       </c>
@@ -2476,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B55" s="3">
         <v>51</v>
       </c>
@@ -2504,8 +2516,11 @@
       <c r="J55" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="Q55" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B56" s="3">
         <v>52</v>
       </c>
@@ -2534,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B57" s="3">
         <v>54</v>
       </c>
@@ -2563,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B58" s="3">
         <v>55</v>
       </c>
@@ -2592,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B59" s="3">
         <v>56</v>
       </c>
@@ -2621,7 +2636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B60" s="3">
         <v>57</v>
       </c>
@@ -2650,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:17" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B61" s="3">
         <v>58</v>
       </c>
@@ -2679,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B62" s="3">
         <v>59</v>
       </c>
@@ -2708,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B63" s="3">
         <v>60</v>
       </c>
@@ -2737,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B64" s="3">
         <v>61</v>
       </c>
@@ -2766,7 +2781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B65" s="3">
         <v>62</v>
       </c>
@@ -2795,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:17" ht="27" x14ac:dyDescent="0.15">
       <c r="B66" s="3">
         <v>63</v>
       </c>
@@ -2824,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B67" s="3">
         <v>64</v>
       </c>
@@ -2853,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B68" s="3">
         <v>65</v>
       </c>
@@ -2882,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B69" s="3">
         <v>66</v>
       </c>
@@ -2911,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B70" s="3">
         <v>67</v>
       </c>
@@ -2940,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B71" s="8">
         <v>68</v>
       </c>
@@ -2968,8 +2983,11 @@
       <c r="J71" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="Q71" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="8">
         <v>69</v>
       </c>
@@ -2998,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B73" s="8">
         <v>70</v>
       </c>
@@ -3027,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B74" s="8">
         <v>71</v>
       </c>
@@ -3056,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B75" s="8">
         <v>72</v>
       </c>
@@ -3085,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B76" s="8">
         <v>73</v>
       </c>
@@ -3114,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:17" s="8" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B77" s="8">
         <v>74</v>
       </c>
@@ -3143,7 +3161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="8">
         <v>75</v>
       </c>
@@ -3172,7 +3190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="8">
         <v>76</v>
       </c>
@@ -3201,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="8">
         <v>77</v>
       </c>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D6D4E0-CBE1-4E10-9411-3096861809F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609B8C7E-53BD-450B-BD82-C9DFC2146484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A56BE3C-BBFE-492C-A1B0-BFF1DB3A5905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEC6547-D478-4585-9A85-D9D09EC86E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEC6547-D478-4585-9A85-D9D09EC86E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BEC7CD-6D8A-4713-B70D-6AAF73918AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="132">
   <si>
     <t>##var</t>
   </si>
@@ -407,6 +407,34 @@
   </si>
   <si>
     <t>idle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看到灯里面伸出两只触须，似乎是蟑螂住在里面</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>要我说，你们还有回本的机会，如果不赌就是把钱全都放弃了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好，我押上这套灯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>出老千</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太好了，你个傻逼把我们的家都输掉了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>think1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>talk2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -816,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
@@ -3265,7 +3293,9 @@
       <c r="N82" s="11"/>
       <c r="O82" s="11"/>
       <c r="P82" s="11"/>
-      <c r="Q82" s="11"/>
+      <c r="Q82" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="R82" s="11"/>
     </row>
     <row r="83" spans="2:18" s="12" customFormat="1" x14ac:dyDescent="0.15">
@@ -3346,7 +3376,7 @@
         <v>1004001</v>
       </c>
       <c r="D85" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>122</v>
@@ -3373,6 +3403,136 @@
       <c r="Q85" s="11"/>
       <c r="R85" s="11"/>
     </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B86" s="12">
+        <v>83</v>
+      </c>
+      <c r="C86" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D86" s="9">
+        <v>0</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I86" s="12">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B87" s="12">
+        <v>84</v>
+      </c>
+      <c r="C87" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D87" s="9">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I87" s="12">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B88" s="12">
+        <v>85</v>
+      </c>
+      <c r="C88" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D88" s="9">
+        <v>2</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I88" s="12">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B89" s="12">
+        <v>86</v>
+      </c>
+      <c r="C89" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D89" s="9">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I89" s="12">
+        <v>0</v>
+      </c>
+      <c r="J89" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B90" s="12">
+        <v>87</v>
+      </c>
+      <c r="C90" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D90" s="9">
+        <v>2</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I90" s="12">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BEC7CD-6D8A-4713-B70D-6AAF73918AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F19BBF-9894-47DE-868A-367CAE5CD6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -386,14 +386,6 @@
     <t>教练对着整个场馆的人大喊，外城人停下了斗殴鼻青脸肿的围在擂台旁边，属于外城的摇滚要开始了。</t>
   </si>
   <si>
-    <t>妈的，连开五把红了，这把我全押黑，概率回归！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>惊人的沉默，你感觉灯光甚至闪了两下，历史垃圾堆从来没有如此寂静。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>我操你妈，就看这一招了，就看这一招了啊！！！</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -410,22 +402,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>你看到灯里面伸出两只触须，似乎是蟑螂住在里面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>要我说，你们还有回本的机会，如果不赌就是把钱全都放弃了</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>好，我押上这套灯</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>出老千</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>太好了，你个傻逼把我们的家都输掉了</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -435,6 +415,34 @@
   </si>
   <si>
     <t>talk2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>妈的，下完这把再也不干了，再也不干了，收回本再也不干了，来！！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>惊人的沉默来了，灯闪了两下，历史垃圾堆在对你闪烁。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看到灯里面伸出两只触须，你知道你的机会来了，要么就是你的精神病犯了，或者二者兼而有之。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先生们，一切都还没有结束。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个光屁股说的有点道理。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你再说鸡吧，我们已经没什么东西可以输了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们不是还他妈的有这盏灯吗？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -844,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
@@ -858,7 +866,9 @@
     <col min="9" max="9" width="21.75" style="9" customWidth="1"/>
     <col min="10" max="10" width="20.125" style="9" customWidth="1"/>
     <col min="11" max="12" width="9" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="9"/>
+    <col min="13" max="16" width="9" style="9"/>
+    <col min="17" max="17" width="16.75" style="9" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.15">
@@ -3261,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:18" s="12" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:18" s="12" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="B82" s="12">
         <v>79</v>
       </c>
@@ -3272,14 +3282,14 @@
         <v>2</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F82" s="11"/>
       <c r="G82" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I82" s="12">
         <v>0</v>
@@ -3309,14 +3319,14 @@
         <v>2</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F83" s="11"/>
       <c r="G83" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H83" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I83" s="12">
         <v>0</v>
@@ -3333,7 +3343,7 @@
       <c r="Q83" s="11"/>
       <c r="R83" s="11"/>
     </row>
-    <row r="84" spans="2:18" s="12" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:18" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="12">
         <v>81</v>
       </c>
@@ -3344,14 +3354,14 @@
         <v>0</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F84" s="11"/>
       <c r="G84" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I84" s="12">
         <v>0</v>
@@ -3376,17 +3386,17 @@
         <v>1004001</v>
       </c>
       <c r="D85" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F85" s="11"/>
       <c r="G85" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H85" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I85" s="12">
         <v>0</v>
@@ -3403,7 +3413,7 @@
       <c r="Q85" s="11"/>
       <c r="R85" s="11"/>
     </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:18" ht="27" x14ac:dyDescent="0.15">
       <c r="B86" s="12">
         <v>83</v>
       </c>
@@ -3414,13 +3424,13 @@
         <v>0</v>
       </c>
       <c r="E86" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="H86" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I86" s="12">
         <v>0</v>
@@ -3440,13 +3450,13 @@
         <v>1</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I87" s="12">
         <v>0</v>
@@ -3463,16 +3473,16 @@
         <v>1004001</v>
       </c>
       <c r="D88" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="I88" s="12">
         <v>0</v>
@@ -3489,16 +3499,16 @@
         <v>1004001</v>
       </c>
       <c r="D89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H89" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="I89" s="12">
         <v>0</v>
@@ -3518,18 +3528,96 @@
         <v>2</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I90" s="12">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B91" s="12">
+        <v>88</v>
+      </c>
+      <c r="C91" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D91" s="9">
+        <v>1</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I91" s="12">
+        <v>0</v>
+      </c>
+      <c r="J91" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B92" s="12">
+        <v>89</v>
+      </c>
+      <c r="C92" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D92" s="9">
+        <v>2</v>
+      </c>
+      <c r="E92" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H90" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I90" s="12">
-        <v>0</v>
-      </c>
-      <c r="J90" s="12">
+      <c r="G92" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I92" s="12">
+        <v>0</v>
+      </c>
+      <c r="J92" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.15">
+      <c r="B93" s="12">
+        <v>90</v>
+      </c>
+      <c r="C93" s="12">
+        <v>1004001</v>
+      </c>
+      <c r="D93" s="9">
+        <v>2</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I93" s="12">
+        <v>0</v>
+      </c>
+      <c r="J93" s="12">
         <v>0</v>
       </c>
     </row>
